--- a/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6B期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6B期.xlsx
@@ -10728,23 +10728,19 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H147" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I147" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="H147" s="5" t="n">
+        <v>31027941</v>
+      </c>
+      <c r="I147" s="5" t="n">
+        <v>33800</v>
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
@@ -10753,12 +10749,12 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L147" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M147" s="3" t="inlineStr">
@@ -10768,7 +10764,7 @@
       </c>
       <c r="N147" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -12286,7 +12282,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -12296,7 +12292,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -13175,12 +13171,12 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>A | 918呎 (3房)
-招标单位
--
-(在售)</t>
+$3103万
+$33,800/呎
+(26年-09月-26日)</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">

--- a/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6B期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6B期.xlsx
@@ -8668,23 +8668,19 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H117" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I117" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="n">
+        <v>37429967</v>
+      </c>
+      <c r="I117" s="5" t="n">
+        <v>40773</v>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
@@ -8693,12 +8689,12 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M117" s="3" t="inlineStr">
@@ -8708,7 +8704,7 @@
       </c>
       <c r="N117" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -12282,7 +12278,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -12292,7 +12288,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -12861,12 +12857,12 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>A | 918呎 (3房)
-招标单位
--
-(在售)</t>
+$3743万
+$40,773/呎
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">

--- a/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6B期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6B期.xlsx
@@ -8673,7 +8673,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -12862,7 +12862,7 @@
           <t>A | 918呎 (3房)
 $3743万
 $40,773/呎
-(26年-09月-30日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">

--- a/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6B期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6B期.xlsx
@@ -10729,7 +10729,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -13172,7 +13172,7 @@
           <t>A | 918呎 (3房)
 $3103万
 $33,800/呎
-(26年-09月-26日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
